--- a/generated/spreadsheet/permission-in-principle-pip.xlsx
+++ b/generated/spreadsheet/permission-in-principle-pip.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,48 +1067,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1114,21 +1122,13 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1136,14 +1136,18 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1153,7 +1157,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1172,13 +1176,13 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1207,13 +1211,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1242,13 +1246,13 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1277,13 +1281,13 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1307,18 +1311,14 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1342,19 +1342,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1364,58 +1364,58 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1439,14 +1439,18 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1456,7 +1460,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1475,18 +1479,18 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1496,51 +1500,47 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1548,14 +1548,18 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1565,7 +1569,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1584,13 +1588,13 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1600,7 +1604,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1623,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1654,13 +1658,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1689,13 +1693,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1705,32 +1709,32 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1740,32 +1744,28 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1789,14 +1789,18 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1806,7 +1810,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1825,18 +1829,18 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1846,54 +1850,54 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1901,12 +1905,12 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1916,19 +1920,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1936,17 +1932,17 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1951,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1963,7 +1959,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1978,11 +1974,19 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1990,7 +1994,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2000,24 +2004,16 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2025,12 +2021,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2044,7 +2040,7 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2052,12 +2048,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2067,11 +2063,19 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposed development including any non-residential development</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential and non-residential parts of the proposed development.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2079,7 +2083,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Description of proposed development including non-residential development</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2094,19 +2098,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposed development including any non-residential development</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential and non-residential parts of the proposed development.</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Net dwellings minimum</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2114,12 +2110,12 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Description of proposed development including non-residential development</t>
+          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2133,7 +2129,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings minimum</t>
+          <t>Net dwellings maximum</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2141,7 +2137,7 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
+          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2160,20 +2156,24 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings maximum</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
+          <t>Non-residential use[]</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Non-residential measurement type</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
+          <t>Type of measurement being provided (floorspace or site-area)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2192,24 +2192,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Non-residential measurement type</t>
+          <t>Exact value</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Type of measurement being provided (floorspace or site-area)</t>
+          <t>Exact figure of non-residential use</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2223,14 +2223,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Exact value</t>
+          <t>Minimum value</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Exact figure of non-residential use</t>
+          <t>Lower bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2254,14 +2254,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Minimum value</t>
+          <t>Maximum value</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Lower bound of non-residential use for ranges</t>
+          <t>Upper bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2276,28 +2276,36 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Maximum value</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Upper bound of non-residential use for ranges</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2307,16 +2315,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2324,19 +2324,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2479,14 +2479,14 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2510,19 +2510,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2541,14 +2541,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2563,47 +2563,47 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Site information</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Any additional relevant information about the development site.</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Numeric value representing a measurement or quantity</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Site information</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Any additional relevant information about the development site.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Site area</t>
@@ -2611,19 +2611,19 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Numeric value representing a measurement or quantity</t>
+          <t>Unit of measurement for a value</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Unit of measurement for a value</t>
+          <t>Whether the information was provided by the applicant or calculated by the system</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2668,19 +2668,23 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Existing use[]</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Whether the information was provided by the applicant or calculated by the system</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2690,7 +2694,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2713,23 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2739,28 +2743,24 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Floorspace</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Total floorspace for a use in square metres</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2769,24 +2769,20 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Floorspace</t>
-        </is>
-      </c>
+          <t>Known constraints[]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Total floorspace for a use in square metres</t>
+          <t>A list of the known constraints affecting the site</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -2800,20 +2796,24 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Known constraints[]</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>A list of the known constraints affecting the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2832,14 +2832,14 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Additional details or information about an item</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -2848,37 +2848,6 @@
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Additional details or information about an item</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -2886,28 +2855,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="A65:A73"/>
-    <mergeCell ref="B20:B27"/>
-    <mergeCell ref="A56:A64"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B65:B73"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="B56:B64"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A20:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B48:B54"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="A55:A63"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B41"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B64:B72"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="A64:A72"/>
+    <mergeCell ref="B19:B26"/>
+    <mergeCell ref="A41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A19:A26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/permission-in-principle-pip.xlsx
+++ b/generated/spreadsheet/permission-in-principle-pip.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">

--- a/generated/spreadsheet/permission-in-principle-pip.xlsx
+++ b/generated/spreadsheet/permission-in-principle-pip.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,52 +1063,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1122,13 +1114,21 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1136,18 +1136,14 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1157,7 +1153,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1176,13 +1172,13 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1192,7 +1188,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1211,13 +1207,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1246,13 +1242,13 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1281,13 +1277,13 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1311,14 +1307,18 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1342,19 +1342,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1364,58 +1364,58 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1439,18 +1439,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1460,7 +1456,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1479,18 +1475,18 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,47 +1496,51 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1548,18 +1548,14 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1569,7 +1565,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1588,13 +1584,13 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1604,7 +1600,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1623,13 +1619,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1658,13 +1654,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1693,13 +1689,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1709,32 +1705,32 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1744,28 +1740,32 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1789,18 +1789,14 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1810,7 +1806,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1829,18 +1825,18 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1850,54 +1846,54 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1905,12 +1901,12 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1920,11 +1916,19 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1932,17 +1936,17 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1955,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1959,7 +1963,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1974,19 +1978,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1994,7 +1990,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2004,16 +2000,24 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2021,12 +2025,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2040,7 +2044,7 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2048,12 +2052,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2063,19 +2067,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposed development including any non-residential development</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential and non-residential parts of the proposed development.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2083,12 +2079,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Description of proposed development including non-residential development</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2098,11 +2094,19 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposed development including any non-residential development</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential and non-residential parts of the proposed development.</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings minimum</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2110,12 +2114,12 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
+          <t>Description of proposed development including non-residential development</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2129,7 +2133,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings maximum</t>
+          <t>Net dwellings minimum</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2137,12 +2141,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
+          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2156,24 +2160,20 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Non-residential measurement type</t>
-        </is>
-      </c>
+          <t>Net dwellings maximum</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Type of measurement being provided (floorspace or site-area)</t>
+          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2192,24 +2192,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Exact value</t>
+          <t>Non-residential measurement type</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Exact figure of non-residential use</t>
+          <t>Type of measurement being provided (floorspace or site-area)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2223,19 +2223,19 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Minimum value</t>
+          <t>Exact value</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Lower bound of non-residential use for ranges</t>
+          <t>Exact figure of non-residential use</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2254,19 +2254,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Maximum value</t>
+          <t>Minimum value</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Upper bound of non-residential use for ranges</t>
+          <t>Lower bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2276,36 +2276,28 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Non-residential use[]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Maximum value</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Upper bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2315,8 +2307,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2324,19 +2324,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2417,19 +2417,19 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2448,19 +2448,19 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2479,19 +2479,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2510,19 +2510,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2541,14 +2541,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2563,47 +2563,47 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Site information</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Any additional relevant information about the development site.</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Numeric value representing a measurement or quantity</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Site information</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Any additional relevant information about the development site.</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Site area</t>
@@ -2611,19 +2611,19 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Unit of measurement for a value</t>
+          <t>Size of the development site area</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Whether the information was provided by the applicant or calculated by the system</t>
+          <t>Unit of measurement for a value</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2668,23 +2668,19 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Provided by</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Whether the information was provided by the applicant or calculated by the system</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2694,7 +2690,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2713,23 +2709,23 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2743,24 +2739,28 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Floorspace</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Specified use</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Total floorspace for a use in square metres</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2769,20 +2769,24 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Known constraints[]</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
+          <t>Existing use[]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Floorspace</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>A list of the known constraints affecting the site</t>
+          <t>Total floorspace for a use in square metres</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -2796,24 +2800,20 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Known constraints[]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A list of the known constraints affecting the site</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2832,22 +2832,53 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
           <t>Additional details or information about an item</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -2855,28 +2886,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="B48:B54"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="A55:A63"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B41"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B64:B72"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="A64:A72"/>
-    <mergeCell ref="B19:B26"/>
-    <mergeCell ref="A41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A19:A26"/>
+    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="A65:A73"/>
+    <mergeCell ref="B20:B27"/>
+    <mergeCell ref="A56:A64"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B49:B55"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B65:B73"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B42"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="B56:B64"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A20:A27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/permission-in-principle-pip.xlsx
+++ b/generated/spreadsheet/permission-in-principle-pip.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1277,13 +1277,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1312,13 +1316,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1342,14 +1350,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1373,19 +1389,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1395,32 +1411,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1430,23 +1442,27 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1456,7 +1472,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1470,18 +1486,14 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1491,7 +1503,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1510,18 +1522,18 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1531,47 +1543,51 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1579,18 +1595,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1600,7 +1612,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1631,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1635,7 +1647,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1654,13 +1666,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1689,13 +1701,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1724,48 +1736,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1775,7 +1795,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1784,19 +1804,27 @@
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1806,32 +1834,32 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1841,7 +1869,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1855,53 +1883,49 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1911,51 +1935,59 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1963,7 +1995,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1973,16 +2005,24 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1990,31 +2030,23 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Person reference</t>
@@ -2025,7 +2057,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2035,7 +2067,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2076,7 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2052,26 +2084,34 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2079,12 +2119,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2094,19 +2134,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposed development including any non-residential development</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential and non-residential parts of the proposed development.</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2114,12 +2146,12 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Description of proposed development including non-residential development</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2133,7 +2165,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings minimum</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2141,12 +2173,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2156,11 +2188,19 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposed development including any non-residential development</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential and non-residential parts of the proposed development.</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings maximum</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2168,12 +2208,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
+          <t>Description of proposed development including non-residential development</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2187,24 +2227,20 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Non-residential measurement type</t>
-        </is>
-      </c>
+          <t>Net dwellings minimum</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Type of measurement being provided (floorspace or site-area)</t>
+          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2218,29 +2254,25 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Exact value</t>
-        </is>
-      </c>
+          <t>Net dwellings maximum</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Exact figure of non-residential use</t>
+          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2254,24 +2286,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Minimum value</t>
+          <t>Non-residential measurement type</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Lower bound of non-residential use for ranges</t>
+          <t>Type of measurement being provided (floorspace or site-area)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2285,14 +2317,14 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Maximum value</t>
+          <t>Exact value</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Upper bound of non-residential use for ranges</t>
+          <t>Exact figure of non-residential use</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2307,36 +2339,28 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Non-residential use[]</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Minimum value</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Lower bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2350,24 +2374,24 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Non-residential use[]</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Maximum value</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Upper bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2377,8 +2401,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2386,24 +2418,24 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2417,24 +2449,28 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2448,19 +2484,23 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2479,19 +2519,23 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2510,19 +2554,23 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2541,19 +2589,19 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2572,19 +2620,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2594,41 +2642,33 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Site information</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Any additional relevant information about the development site.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Size of the development site area</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2637,35 +2677,43 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Unit of measurement for a value</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Site information</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Any additional relevant information about the development site.</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Site area</t>
@@ -2673,24 +2721,24 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Whether the information was provided by the applicant or calculated by the system</t>
+          <t>Size of the development site area</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2699,28 +2747,24 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Unit of measurement for a value</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2734,28 +2778,24 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Provided by</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Whether the information was provided by the applicant or calculated by the system</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2774,19 +2814,23 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Floorspace</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Total floorspace for a use in square metres</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -2800,25 +2844,33 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Known constraints[]</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
+          <t>Existing use[]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Specified use</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>A list of the known constraints affecting the site</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2827,24 +2879,24 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Existing use[]</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Floorspace</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Total floorspace for a use in square metres</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2858,27 +2910,85 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
+          <t>Known constraints[]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
+          <t>A list of the known constraints affecting the site</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
           <t>Additional details or information about an item</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -2886,28 +2996,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="A65:A73"/>
-    <mergeCell ref="B20:B27"/>
-    <mergeCell ref="A56:A64"/>
+    <mergeCell ref="B67:B75"/>
+    <mergeCell ref="B58:B66"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B65:B73"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="B56:B64"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A20:A27"/>
-    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="B33:B39"/>
+    <mergeCell ref="A20:A28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B51:B57"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B20:B28"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="A67:A75"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="A51:A57"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42"/>
+    <mergeCell ref="A40:A43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
